--- a/sample-data/ai-cashflow-variants/02-nha-hang-bep-viet-36/input/02_nhat_ky_thu_chi.xlsx
+++ b/sample-data/ai-cashflow-variants/02-nha-hang-bep-viet-36/input/02_nhat_ky_thu_chi.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R607158bc26254296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhật ký 90 ngày" sheetId="2" r:id="R0ebaff17995e4ab3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R8240e979b1f04c98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhật ký 90 ngày" sheetId="2" r:id="R195fa6c6e87f4aa4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/sample-data/ai-cashflow-variants/02-nha-hang-bep-viet-36/input/02_nhat_ky_thu_chi.xlsx
+++ b/sample-data/ai-cashflow-variants/02-nha-hang-bep-viet-36/input/02_nhat_ky_thu_chi.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="R8240e979b1f04c98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhật ký 90 ngày" sheetId="2" r:id="R195fa6c6e87f4aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Đọc trước" sheetId="1" r:id="Rfb12a7f4aec64c12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhật ký 90 ngày" sheetId="2" r:id="R0dab8ac6dc5a48e4"/>
   </x:sheets>
 </x:workbook>
 </file>
